--- a/실습폴더/3 웹 작업 - 학습준비물/학습준비물 빈 양식.xlsx
+++ b/실습폴더/3 웹 작업 - 학습준비물/학습준비물 빈 양식.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -466,106 +466,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>독도의날 만들기 키트</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1인용</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>24</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>아이스크림몰</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>한글날 만들기 키트</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1인용</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>아이스크림몰</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>크리스마스 만들기 키트</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1인용</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>24</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>아이스크림몰</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>물티슈</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>캡형 70~100매, 10팩 묶음</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>아이스크림몰</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>각티슈</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>200매 이상, 6개 이상 묶음</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>아이스크림몰</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
